--- a/database/seed/grocery.xlsx
+++ b/database/seed/grocery.xlsx
@@ -440,7 +440,7 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>BizFlow workbook</x:v>
+        <x:v>Shay Sett workbook</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
         <x:v>Input instructions</x:v>
